--- a/site/exports/nju-philosophy.xlsx
+++ b/site/exports/nju-philosophy.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,12 +443,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="18.2" customWidth="1" min="3" max="3"/>
+    <col width="19.6" customWidth="1" min="3" max="3"/>
     <col width="65" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
@@ -569,10 +569,118 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>孙乐强</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>哲学学院</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>https://philo.nju.edu.cn/f3/b0/c4712a127920/page.htm</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>哲学学院个人页列教授、博导，历史IAS页列哲学系、马克思主义学院副教授；各来源单位和职称不同，不猜晋升或更名、当前身份。；个人页显示2016-04-27，IAS页显示2018-09-17，是来源显示日期，不认证最后修改或职业标签时序。；IAS来源标题第十三期驻院学者（2017年9月–2018年8月）保留，不凭栏目标题新增独立任职。；2004教育学学士、2007哲学硕士、2010法学博士均原明确获授，只有年精度；2008–2009访问师从特瑞尔·卡弗不作学位论文导师。；本批未选具名作品，0不等于本人没有论文或著作；原任职数组空不否认官网职业身份。</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>nju</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>南京大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>包蕾</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>哲学系（宗教学系）宗教学学科</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>https://philo.nju.edu.cn/c2/10/c4712a508432/page.htm</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>原2020年12月至今南京大学哲学系（宗教学系）宗教学学科关联未列具体岗位，不推讲师、副教授或当前聘任；保留独立未分类机构区间，不造任职记录。；本科双学位是一个共同区间及两个原资格称谓；硕士、博士原各阶段与具体资格同时保留，不将区间结束直接当授位日。；博士论文原题《&lt;解深密经&gt;的真理观》（The Theory of Truth in the Saṃdhinirmocana-sūtra），未读论文、不认证答辩或导师；杨维中仅博士后合作导师。；两篇作品的期刊与年月按原个人清单保留，作者完整串与独著未知，未外核出版者或全文。</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>nju</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>南京大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K2"/>
+  <autoFilter ref="A1:K4"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -584,12 +692,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:S12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="25.2" customWidth="1" min="2" max="2"/>
+    <col width="19.6" customWidth="1" min="3" max="3"/>
     <col width="37.8" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
@@ -914,12 +1022,544 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>孙乐强</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>教育学学士</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学哲学与社会学学院</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>2004毕业于北京师范大学哲学与社会学学院并明确获教育学学士，学位类别按原不改为哲学；原授位日期精度为年。</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>https://ias.nju.edu.cn/84/f5/c13141a296181/page.htm</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>nju</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>南京大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>孙乐强</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>哲学硕士</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>南京大学哲学系</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>2007毕业于南京大学哲学系并明确获哲学硕士；授位只到年，不补月日或起学年。</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>https://ias.nju.edu.cn/84/f5/c13141a296181/page.htm</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>nju</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>南京大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>孙乐强</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>法学博士</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>南京大学哲学系</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>2010毕业于南京大学哲学系并明确获法学博士，不能因哲学机构改成哲学博士；授位只到年。</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>https://ias.nju.edu.cn/84/f5/c13141a296181/page.htm</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>nju</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>南京大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>孙乐强</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>nondegree_training</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>英国布里斯托大学政治系</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>2008–2009英国布里斯托大学政治系访问学习，明确师从特瑞尔·卡弗；是非学位访问阶段师承，不是博士论文导师。</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>https://ias.nju.edu.cn/84/f5/c13141a296181/page.htm</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>nju</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>南京大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>包蕾</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>哲学学士、法学学士（双学位）</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>南京大学哲学系（宗教学系）</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2005年9月</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2009年6月</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>2005年9月至2009年6月本科阶段，南京大学哲学系（宗教学系），原列哲学学士、法学学士（双学位）；保持一个共同学习事件及两资格称谓，不拆两个日期或推法律双学位制度。</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>https://philo.nju.edu.cn/c2/10/c4712a508432/page.htm</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>nju</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>南京大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>包蕾</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>哲学硕士</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>南京大学哲学系（宗教学系）</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2009年9月</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2012年6月</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>中国哲学</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>2009年9月至2012年6月硕士研究生阶段，南京大学哲学系（宗教学系）中国哲学专业，原具体列哲学硕士；学习区间不当授位日期。</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>https://philo.nju.edu.cn/c2/10/c4712a508432/page.htm</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>nju</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>南京大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>包蕾</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>哲学博士</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>台湾大学文学院哲学系</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2012年9月</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2017年8月</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>2012年9月至2017年8月博士研究生阶段，台湾大学文学院哲学系，原具体列哲学博士；原博士论文题名另存，不由题名推导师或授位日期。</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>https://philo.nju.edu.cn/c2/10/c4712a508432/page.htm</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>nju</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>南京大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>包蕾</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>nondegree_training</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>南京大学哲学系（宗教学系）</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2017年12月</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2020年11月</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>宗教学</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>2017年12月至2020年11月南京大学哲学系（宗教学系）宗教学学科统招统分博士后，合作导师杨维中教授；非学位，不转博士论文导师。</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>https://philo.nju.edu.cn/c2/10/c4712a508432/page.htm</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>nju</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>南京大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S4"/>
+  <autoFilter ref="A1:S12"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -931,18 +1571,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="54.59999999999999" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="65" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
@@ -1010,8 +1650,112 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>孙乐强</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>特瑞尔·卡弗</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>访问学习（非学位）导师（非原论文核验）</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>访问学习（非学位）</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>原明确访问学习（非学位）关系；未读原学位论文，未解析导师身份节点或认证现职。</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>https://ias.nju.edu.cn/84/f5/c13141a296181/page.htm</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>nju</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>南京大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>包蕾</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>杨维中</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>博士后合作（非学位）导师（非原论文核验）</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>博士后合作（非学位）</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>原明确博士后合作（非学位）关系；未读原学位论文，未解析导师身份节点或认证现职。</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>https://philo.nju.edu.cn/c2/10/c4712a508432/page.htm</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>nju</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>南京大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:L3"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1022,19 +1766,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="30.8" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="65" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="65" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
   </cols>
@@ -1101,8 +1845,96 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>包蕾</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>“解经”与“教制”视域融合下的佛教中国化研究</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>期刊论文（来源书目）</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>https://philo.nju.edu.cn/c2/10/c4712a508432/page.htm</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>原个人成果清单，法音，2019年12月；完整作者未列，个人页归属不证明独著或作者顺序；未核出版者及全文。</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>nju</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>南京大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>包蕾</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>魏晋哲学对“语言”之反思——以王弼和僧肇为例</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>期刊论文（来源书目）</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>https://philo.nju.edu.cn/c2/10/c4712a508432/page.htm</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>原个人成果清单，哲学分析，2018年12月；完整作者未列，个人页归属不证明独著或作者顺序；未核出版者及全文。</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>nju</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>南京大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:L3"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1113,11 +1945,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="19.6" customWidth="1" min="2" max="2"/>
+    <col width="25.2" customWidth="1" min="2" max="2"/>
     <col width="65" customWidth="1" min="3" max="3"/>
     <col width="53.2" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -1199,10 +2031,112 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>孙乐强</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>nju-sunleqiang</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>https://philo.nju.edu.cn/f3/b0/c4712a127920/page.htm</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>nju</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>南京大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>孙乐强</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>nju-sunleqiang-ias</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>https://ias.nju.edu.cn/84/f5/c13141a296181/page.htm</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>nju</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>南京大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>包蕾</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>profile-2-392</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>https://philo.nju.edu.cn/c2/10/c4712a508432/page.htm</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>nju</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>南京大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:G5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
